--- a/quan-ly-du-an/vi-du-httt.xlsx
+++ b/quan-ly-du-an/vi-du-httt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Esclipe_Web\Quan ly du an HTTT\quan-ly-du-an\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFBA858-818C-44E9-8205-8F5E45617024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0B2752-3E11-49D2-8677-4AE2CDE048DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="120">
   <si>
     <t>LỊCH TRÌNH DỰ ÁN CỔNG ĐĂNG KÝ DỊCH VỤ TRỰC TUYẾN (ước lượng ba điểm, PERT)</t>
   </si>
@@ -217,6 +217,9 @@
     <t>Độ nhạy MC (ngày)</t>
   </si>
   <si>
+    <t>Đóng góp kỳ vọng (ngày)</t>
+  </si>
+  <si>
     <t>R1</t>
   </si>
   <si>
@@ -359,6 +362,18 @@
   </si>
   <si>
     <t>Có rủi ro</t>
+  </si>
+  <si>
+    <t>Đến ngày</t>
+  </si>
+  <si>
+    <t>Số lần (không rủi ro)</t>
+  </si>
+  <si>
+    <t>Số lần (có rủi ro)</t>
+  </si>
+  <si>
+    <t>Tích lũy (có rủi ro)</t>
   </si>
   <si>
     <t>Trung bình (ngày)</t>
@@ -481,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -508,10 +523,16 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -557,6 +578,807 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Đóng góp kỳ vọng của từng rủi ro vào thời gian dự án (ngày)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sổ rủi ro'!$P$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Đóng góp kỳ vọng (ngày)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sổ rủi ro'!$A$5:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>R1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>R2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>R3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>R4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>R5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>R6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>R7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>R8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>R9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>R10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>R11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>R12</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sổ rủi ro'!$P$5:$P$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>3.8840000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3969999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.11549999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3840000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.1125</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.587</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0409999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.675</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.024</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.49199999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B261-4582-9B25-02F34EC02640}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Phân phối thời gian hoàn thành (10.000 lần mô phỏng)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Monte Carlo'!$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Số lần (không rủi ro)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Monte Carlo'!$E$5:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monte Carlo'!$F$5:$F$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1644</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3528</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3130</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1237</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6566-4B4D-BF44-26222E41FC72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Monte Carlo'!$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Số lần (có rủi ro)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Monte Carlo'!$E$5:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>170</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monte Carlo'!$G$5:$G$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>293</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>678</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1234</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1619</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1762</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1541</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1136</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>801</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>118</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6566-4B4D-BF44-26222E41FC72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Monte Carlo'!$H$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tích lũy (có rủi ro)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monte Carlo'!$H$5:$H$22</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.8999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.6200000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.22739999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.38929999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.5655</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.71960000000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.83320000000000005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.9133</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95830000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.98229999999999995</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.99409999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.99770000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.99909999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.99980000000000002</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6566-4B4D-BF44-26222E41FC72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="10"/>
+        <c:axId val="200"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5760000" cy="3240000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7200000" cy="3240000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1313,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1326,19 +2148,20 @@
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="10" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1384,21 +2207,24 @@
       <c r="O4" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P4" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="12">
+        <v>64</v>
+      </c>
+      <c r="E5" s="13">
         <v>0.4</v>
       </c>
       <c r="F5" s="6">
@@ -1423,7 +2249,7 @@
         <f t="shared" ref="K5:K16" si="3">IF(H5&lt;3,1,IF(H5&lt;5,2,IF(H5&lt;7,3,IF(H5&lt;10,4,5))))</f>
         <v>5</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="14">
         <f t="shared" ref="L5:L16" si="4">J5*K5</f>
         <v>25</v>
       </c>
@@ -1437,21 +2263,25 @@
       <c r="O5" s="7">
         <v>9.7100000000000009</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P5" s="15">
+        <f t="shared" ref="P5:P16" si="6">E5*O5</f>
+        <v>3.8840000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="12">
+        <v>67</v>
+      </c>
+      <c r="E6" s="13">
         <v>0.35</v>
       </c>
       <c r="F6" s="6">
@@ -1476,7 +2306,7 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="14">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -1490,21 +2320,25 @@
       <c r="O6" s="7">
         <v>4.9800000000000004</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P6" s="15">
+        <f t="shared" si="6"/>
+        <v>1.7430000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="12">
+        <v>71</v>
+      </c>
+      <c r="E7" s="13">
         <v>0.3</v>
       </c>
       <c r="F7" s="6">
@@ -1529,7 +2363,7 @@
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="14">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
@@ -1543,21 +2377,25 @@
       <c r="O7" s="7">
         <v>7.99</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P7" s="15">
+        <f t="shared" si="6"/>
+        <v>2.3969999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="12">
+        <v>75</v>
+      </c>
+      <c r="E8" s="13">
         <v>0.35</v>
       </c>
       <c r="F8" s="6">
@@ -1582,7 +2420,7 @@
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="14">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
@@ -1596,21 +2434,25 @@
       <c r="O8" s="7">
         <v>0.33</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P8" s="15">
+        <f t="shared" si="6"/>
+        <v>0.11549999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="12">
+        <v>79</v>
+      </c>
+      <c r="E9" s="13">
         <v>0.2</v>
       </c>
       <c r="F9" s="6">
@@ -1635,7 +2477,7 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="14">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
@@ -1649,21 +2491,25 @@
       <c r="O9" s="7">
         <v>6.92</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P9" s="15">
+        <f t="shared" si="6"/>
+        <v>1.3840000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>0.25</v>
       </c>
       <c r="F10" s="6">
@@ -1688,7 +2534,7 @@
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="14">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -1702,21 +2548,25 @@
       <c r="O10" s="7">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P10" s="15">
+        <f t="shared" si="6"/>
+        <v>0.1125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="12">
+        <v>86</v>
+      </c>
+      <c r="E11" s="13">
         <v>0.3</v>
       </c>
       <c r="F11" s="6">
@@ -1741,7 +2591,7 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="14">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -1755,21 +2605,25 @@
       <c r="O11" s="7">
         <v>5.29</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P11" s="15">
+        <f t="shared" si="6"/>
+        <v>1.587</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <v>0.15</v>
       </c>
       <c r="F12" s="6">
@@ -1794,7 +2648,7 @@
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="14">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
@@ -1808,21 +2662,25 @@
       <c r="O12" s="7">
         <v>6.94</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P12" s="15">
+        <f t="shared" si="6"/>
+        <v>1.0409999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <v>0.3</v>
       </c>
       <c r="F13" s="6">
@@ -1847,7 +2705,7 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="14">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
@@ -1861,21 +2719,25 @@
       <c r="O13" s="7">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P13" s="15">
+        <f t="shared" si="6"/>
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="12">
+        <v>96</v>
+      </c>
+      <c r="E14" s="13">
         <v>0.25</v>
       </c>
       <c r="F14" s="6">
@@ -1900,7 +2762,7 @@
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="14">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -1914,21 +2776,25 @@
       <c r="O14" s="7">
         <v>6.7</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="P14" s="15">
+        <f t="shared" si="6"/>
+        <v>1.675</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="12">
+        <v>99</v>
+      </c>
+      <c r="E15" s="13">
         <v>0.4</v>
       </c>
       <c r="F15" s="6">
@@ -1953,7 +2819,7 @@
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="14">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
@@ -1967,21 +2833,25 @@
       <c r="O15" s="7">
         <v>7.56</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="15">
+        <f t="shared" si="6"/>
+        <v>3.024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <v>0.05</v>
       </c>
       <c r="F16" s="6">
@@ -2006,7 +2876,7 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="14">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
@@ -2020,12 +2890,16 @@
       <c r="O16" s="7">
         <v>9.84</v>
       </c>
+      <c r="P16" s="15">
+        <f t="shared" si="6"/>
+        <v>0.49199999999999999</v>
+      </c>
     </row>
     <row r="18" spans="3:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="C18" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="I18" s="15">
+      <c r="C18" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I18" s="17">
         <f>SUM(I5:I16)</f>
         <v>23.375</v>
       </c>
@@ -2043,42 +2917,57 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B5" s="7">
         <v>99.608999999999995</v>
@@ -2086,10 +2975,23 @@
       <c r="C5" s="7">
         <v>118.855</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E5" s="4">
+        <v>85</v>
+      </c>
+      <c r="F5" s="4">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9">
+        <f>SUM($G$5:G5)/SUM($G$5:$G$22)</f>
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B6" s="7">
         <v>5.085</v>
@@ -2097,10 +2999,23 @@
       <c r="C6" s="7">
         <v>11.391</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E6" s="4">
+        <v>90</v>
+      </c>
+      <c r="F6" s="4">
+        <v>216</v>
+      </c>
+      <c r="G6" s="4">
+        <v>11</v>
+      </c>
+      <c r="H6" s="9">
+        <f>SUM($G$5:G6)/SUM($G$5:$G$22)</f>
+        <v>1.1999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B7" s="7">
         <v>99.492000000000004</v>
@@ -2108,10 +3023,23 @@
       <c r="C7" s="7">
         <v>118.215</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E7" s="4">
+        <v>95</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1644</v>
+      </c>
+      <c r="G7" s="4">
+        <v>57</v>
+      </c>
+      <c r="H7" s="9">
+        <f>SUM($G$5:G7)/SUM($G$5:$G$22)</f>
+        <v>6.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B8" s="7">
         <v>103.907</v>
@@ -2119,10 +3047,23 @@
       <c r="C8" s="7">
         <v>128.22399999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E8" s="4">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3528</v>
+      </c>
+      <c r="G8" s="4">
+        <v>293</v>
+      </c>
+      <c r="H8" s="9">
+        <f>SUM($G$5:G8)/SUM($G$5:$G$22)</f>
+        <v>3.6200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B9" s="7">
         <v>106.18600000000001</v>
@@ -2130,10 +3071,23 @@
       <c r="C9" s="7">
         <v>134.10900000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E9" s="4">
+        <v>105</v>
+      </c>
+      <c r="F9" s="4">
+        <v>3130</v>
+      </c>
+      <c r="G9" s="4">
+        <v>678</v>
+      </c>
+      <c r="H9" s="9">
+        <f>SUM($G$5:G9)/SUM($G$5:$G$22)</f>
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B10" s="9">
         <v>0.187</v>
@@ -2141,17 +3095,209 @@
       <c r="C10" s="9">
         <v>7.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="15">
+      <c r="E10" s="4">
+        <v>110</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1237</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1234</v>
+      </c>
+      <c r="H10" s="9">
+        <f>SUM($G$5:G10)/SUM($G$5:$G$22)</f>
+        <v>0.22739999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E11" s="4">
+        <v>115</v>
+      </c>
+      <c r="F11" s="4">
+        <v>219</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1619</v>
+      </c>
+      <c r="H11" s="9">
+        <f>SUM($G$5:G11)/SUM($G$5:$G$22)</f>
+        <v>0.38929999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="17">
         <f>C8-'Lịch trình'!C19</f>
         <v>38.22399999999999</v>
       </c>
+      <c r="E12" s="4">
+        <v>120</v>
+      </c>
+      <c r="F12" s="4">
+        <v>15</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1762</v>
+      </c>
+      <c r="H12" s="9">
+        <f>SUM($G$5:G12)/SUM($G$5:$G$22)</f>
+        <v>0.5655</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E13" s="4">
+        <v>125</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1541</v>
+      </c>
+      <c r="H13" s="9">
+        <f>SUM($G$5:G13)/SUM($G$5:$G$22)</f>
+        <v>0.71960000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E14" s="4">
+        <v>130</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1136</v>
+      </c>
+      <c r="H14" s="9">
+        <f>SUM($G$5:G14)/SUM($G$5:$G$22)</f>
+        <v>0.83320000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E15" s="4">
+        <v>135</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>801</v>
+      </c>
+      <c r="H15" s="9">
+        <f>SUM($G$5:G15)/SUM($G$5:$G$22)</f>
+        <v>0.9133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E16" s="4">
+        <v>140</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>450</v>
+      </c>
+      <c r="H16" s="9">
+        <f>SUM($G$5:G16)/SUM($G$5:$G$22)</f>
+        <v>0.95830000000000004</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E17" s="4">
+        <v>145</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>240</v>
+      </c>
+      <c r="H17" s="9">
+        <f>SUM($G$5:G17)/SUM($G$5:$G$22)</f>
+        <v>0.98229999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E18" s="4">
+        <v>150</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>118</v>
+      </c>
+      <c r="H18" s="9">
+        <f>SUM($G$5:G18)/SUM($G$5:$G$22)</f>
+        <v>0.99409999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E19" s="4">
+        <v>155</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>36</v>
+      </c>
+      <c r="H19" s="9">
+        <f>SUM($G$5:G19)/SUM($G$5:$G$22)</f>
+        <v>0.99770000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E20" s="4">
+        <v>160</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>14</v>
+      </c>
+      <c r="H20" s="9">
+        <f>SUM($G$5:G20)/SUM($G$5:$G$22)</f>
+        <v>0.99909999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E21" s="4">
+        <v>165</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>7</v>
+      </c>
+      <c r="H21" s="9">
+        <f>SUM($G$5:G21)/SUM($G$5:$G$22)</f>
+        <v>0.99980000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E22" s="4">
+        <v>170</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>2</v>
+      </c>
+      <c r="H22" s="9">
+        <f>SUM($G$5:G22)/SUM($G$5:$G$22)</f>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>